--- a/diseases/d042/2026-2029.xlsx
+++ b/diseases/d042/2026-2029.xlsx
@@ -13260,13 +13260,13 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -14096,7 +14096,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3495</v>
+        <v>3496</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d042/2026-2029.xlsx
+++ b/diseases/d042/2026-2029.xlsx
@@ -13221,12 +13221,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -13260,13 +13260,16 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="O88" t="n">
-        <v>1</v>
+        <v>20</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>0.001937969923792046</v>
+        <v>0.001415514231387749</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -13299,42 +13302,42 @@
       </c>
       <c r="AV88" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC88" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -13366,12 +13369,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -13405,13 +13408,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O89" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R89" t="n">
-        <v>0.0008595114398308156</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -13444,42 +13447,42 @@
       </c>
       <c r="AV89" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB89" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC89" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -13541,7 +13544,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -13656,12 +13659,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -13686,22 +13689,22 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O91" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>0.0008595114398308156</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -13734,42 +13737,42 @@
       </c>
       <c r="AV91" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB91" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC91" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -13801,12 +13804,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -13879,42 +13882,332 @@
       </c>
       <c r="AV92" t="inlineStr">
         <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA92" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB92" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC92" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>leprosy</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>麻风病</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N93" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0</v>
+      </c>
+      <c r="R93" t="n">
+        <v>0</v>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP93" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR93" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS93" t="inlineStr"/>
+      <c r="AT93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV93" t="inlineStr">
+        <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW92" t="inlineStr">
+      <c r="AW93" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX92" t="inlineStr">
+      <c r="AX93" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY92" t="inlineStr">
+      <c r="AY93" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ92" t="inlineStr">
+      <c r="AZ93" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA92" t="inlineStr">
+      <c r="BA93" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB92" t="inlineStr">
+      <c r="BB93" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC92" t="inlineStr">
+      <c r="BC93" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>leprosy</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>麻风病</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N94" t="n">
+        <v>1</v>
+      </c>
+      <c r="O94" t="n">
+        <v>1</v>
+      </c>
+      <c r="R94" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP94" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR94" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS94" t="inlineStr"/>
+      <c r="AT94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV94" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA94" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB94" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC94" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -13951,7 +14244,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14327,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10">
@@ -14044,7 +14337,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11">
@@ -14096,7 +14389,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3496</v>
+        <v>3517</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d042/2026-2029.xlsx
+++ b/diseases/d042/2026-2029.xlsx
@@ -13988,13 +13988,13 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>0.003875939847584092</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3517</v>
+        <v>3519</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d042/2026-2029.xlsx
+++ b/diseases/d042/2026-2029.xlsx
@@ -13369,12 +13369,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -13408,13 +13408,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>0.001937969923792046</v>
+        <v>0</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -13447,42 +13447,42 @@
       </c>
       <c r="AV89" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB89" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC89" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -13514,12 +13514,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -13553,13 +13553,13 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O90" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R90" t="n">
-        <v>0.0008595114398308156</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -13592,42 +13592,42 @@
       </c>
       <c r="AV90" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB90" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC90" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -13689,7 +13689,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -13804,12 +13804,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -13834,22 +13834,22 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O92" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>0.0008595114398308156</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -13882,42 +13882,42 @@
       </c>
       <c r="AV92" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB92" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC92" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -13949,12 +13949,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -13988,13 +13988,13 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>0.003875939847584092</v>
+        <v>0</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
@@ -14027,42 +14027,42 @@
       </c>
       <c r="AV93" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB93" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC93" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -14094,12 +14094,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -14124,7 +14124,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -14133,13 +14133,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R94" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0.003875939847584092</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -14172,40 +14172,185 @@
       </c>
       <c r="AV94" t="inlineStr">
         <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA94" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB94" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC94" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>leprosy</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>麻风病</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N95" t="n">
+        <v>1</v>
+      </c>
+      <c r="O95" t="n">
+        <v>1</v>
+      </c>
+      <c r="R95" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP95" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR95" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS95" t="inlineStr"/>
+      <c r="AT95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV95" t="inlineStr">
+        <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW94" t="inlineStr">
+      <c r="AW95" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX94" t="inlineStr">
+      <c r="AX95" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY94" t="inlineStr">
+      <c r="AY95" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ94" t="inlineStr">
+      <c r="AZ95" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA94" t="inlineStr">
+      <c r="BA95" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB94" t="inlineStr">
+      <c r="BB95" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC94" t="inlineStr">
+      <c r="BC95" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -14327,7 +14472,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10">
@@ -14337,7 +14482,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d042/2026-2029.xlsx
+++ b/diseases/d042/2026-2029.xlsx
@@ -21336,12 +21336,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -21375,16 +21375,13 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>20</v>
+        <v>1500</v>
       </c>
       <c r="O130" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q130" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="R130" t="n">
-        <v>0.001415514231387749</v>
+        <v>0.7023699528494134</v>
       </c>
       <c r="S130" t="inlineStr">
         <is>
@@ -21417,42 +21414,42 @@
       </c>
       <c r="AV130" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="BB130" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="BC130" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
     </row>
@@ -21484,12 +21481,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>CN-CQ</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Chongqing, China</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -21523,87 +21520,84 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O131" t="n">
-        <v>0</v>
+        <v>20</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.001415514231387749</v>
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="AA131" t="inlineStr">
-        <is>
-          <t>monthly</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AO131" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>priority_overlay</t>
-        </is>
-      </c>
-      <c r="AQ131" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS131" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_LEPROSY; SER_CN_PROV_REPORT_LEPROSY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR131" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS131" t="inlineStr"/>
       <c r="AT131" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
-          <t>cn_province_datacenter</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>cn_province_datacenter; cn_province_monthly_report</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB131" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC131" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -21630,7 +21624,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -21679,98 +21673,15 @@
       <c r="O132" t="n">
         <v>0</v>
       </c>
-      <c r="U132" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_REPORT_LEPROSY</t>
-        </is>
-      </c>
-      <c r="V132" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_REPORT_LEPROSY</t>
-        </is>
-      </c>
-      <c r="W132" t="inlineStr">
-        <is>
-          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
-        </is>
-      </c>
-      <c r="X132" t="inlineStr">
-        <is>
-          <t>麻风病</t>
-        </is>
-      </c>
-      <c r="Y132" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>provincial_statutory_infectious_disease_monthly_report</t>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>country:CN-CQ:national</t>
-        </is>
-      </c>
-      <c r="AD132" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE132" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF132" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG132" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH132" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI132" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ132" t="inlineStr">
-        <is>
-          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
-        </is>
-      </c>
-      <c r="AK132" t="inlineStr">
-        <is>
-          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
-        </is>
-      </c>
-      <c r="AM132" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN132" t="b">
-        <v>1</v>
       </c>
       <c r="AO132" t="inlineStr">
         <is>
@@ -21864,17 +21775,17 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>CN-GD</t>
+          <t>CN-CQ</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Guangdong, China</t>
+          <t>Chongqing, China</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -21908,20 +21819,103 @@
         </is>
       </c>
       <c r="N133" t="n">
+        <v>0</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0</v>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_LEPROSY</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_LEPROSY</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X133" t="inlineStr">
+        <is>
+          <t>麻风病</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>country:CN-CQ:national</t>
+        </is>
+      </c>
+      <c r="AD133" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE133" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF133" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG133" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH133" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI133" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ133" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK133" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM133" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN133" t="b">
         <v>1</v>
-      </c>
-      <c r="O133" t="n">
-        <v>1</v>
-      </c>
-      <c r="S133" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="AA133" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
       </c>
       <c r="AO133" t="inlineStr">
         <is>
@@ -21983,7 +21977,7 @@
       </c>
       <c r="BB133" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
         </is>
       </c>
       <c r="BC133" t="inlineStr">
@@ -22015,7 +22009,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -22064,98 +22058,15 @@
       <c r="O134" t="n">
         <v>1</v>
       </c>
-      <c r="U134" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_REPORT_LEPROSY</t>
-        </is>
-      </c>
-      <c r="V134" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_REPORT_LEPROSY</t>
-        </is>
-      </c>
-      <c r="W134" t="inlineStr">
-        <is>
-          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
-        </is>
-      </c>
-      <c r="X134" t="inlineStr">
-        <is>
-          <t>麻风病</t>
-        </is>
-      </c>
-      <c r="Y134" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z134" t="inlineStr">
-        <is>
-          <t>provincial_statutory_infectious_disease_monthly_report</t>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB134" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>country:CN-GD:national</t>
-        </is>
-      </c>
-      <c r="AD134" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE134" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF134" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG134" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH134" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI134" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ134" t="inlineStr">
-        <is>
-          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
-        </is>
-      </c>
-      <c r="AK134" t="inlineStr">
-        <is>
-          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
-        </is>
-      </c>
-      <c r="AM134" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN134" t="b">
-        <v>1</v>
       </c>
       <c r="AO134" t="inlineStr">
         <is>
@@ -22249,17 +22160,17 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>CN-HN</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hunan, China</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -22293,20 +22204,103 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O135" t="n">
-        <v>0</v>
-      </c>
-      <c r="S135" t="inlineStr">
-        <is>
-          <t>missing_population</t>
+        <v>1</v>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_LEPROSY</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_LEPROSY</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X135" t="inlineStr">
+        <is>
+          <t>麻风病</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>country:CN-GD:national</t>
+        </is>
+      </c>
+      <c r="AD135" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE135" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF135" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG135" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH135" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI135" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ135" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK135" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM135" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN135" t="b">
+        <v>1</v>
       </c>
       <c r="AO135" t="inlineStr">
         <is>
@@ -22368,7 +22362,7 @@
       </c>
       <c r="BB135" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC135" t="inlineStr">
@@ -22400,7 +22394,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -22449,98 +22443,15 @@
       <c r="O136" t="n">
         <v>0</v>
       </c>
-      <c r="U136" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_REPORT_LEPROSY</t>
-        </is>
-      </c>
-      <c r="V136" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_REPORT_LEPROSY</t>
-        </is>
-      </c>
-      <c r="W136" t="inlineStr">
-        <is>
-          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
-        </is>
-      </c>
-      <c r="X136" t="inlineStr">
-        <is>
-          <t>麻风病</t>
-        </is>
-      </c>
-      <c r="Y136" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z136" t="inlineStr">
-        <is>
-          <t>provincial_statutory_infectious_disease_monthly_report</t>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>country:CN-HN:national</t>
-        </is>
-      </c>
-      <c r="AD136" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE136" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF136" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG136" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH136" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI136" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ136" t="inlineStr">
-        <is>
-          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
-        </is>
-      </c>
-      <c r="AK136" t="inlineStr">
-        <is>
-          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
-        </is>
-      </c>
-      <c r="AM136" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN136" t="b">
-        <v>1</v>
       </c>
       <c r="AO136" t="inlineStr">
         <is>
@@ -22634,17 +22545,17 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -22683,21 +22594,99 @@
       <c r="O137" t="n">
         <v>0</v>
       </c>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="U137" t="inlineStr">
         <is>
           <t>SER_CN_PROV_REPORT_LEPROSY</t>
         </is>
       </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_LEPROSY</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X137" t="inlineStr">
+        <is>
+          <t>麻风病</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>country:CN-HN:national</t>
+        </is>
+      </c>
+      <c r="AD137" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE137" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF137" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG137" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ137" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK137" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM137" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN137" t="b">
+        <v>1</v>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -22705,7 +22694,7 @@
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ137" t="inlineStr">
@@ -22715,15 +22704,15 @@
       </c>
       <c r="AS137" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_REPORT_LEPROSY</t>
+          <t>SER_CN_PROV_DC_LEPROSY; SER_CN_PROV_REPORT_LEPROSY</t>
         </is>
       </c>
       <c r="AT137" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
@@ -22758,7 +22747,7 @@
       </c>
       <c r="BB137" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC137" t="inlineStr">
@@ -22790,7 +22779,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -22839,98 +22828,20 @@
       <c r="O138" t="n">
         <v>0</v>
       </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U138" t="inlineStr">
         <is>
           <t>SER_CN_PROV_REPORT_LEPROSY</t>
         </is>
       </c>
-      <c r="V138" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_REPORT_LEPROSY</t>
-        </is>
-      </c>
-      <c r="W138" t="inlineStr">
-        <is>
-          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
-        </is>
-      </c>
-      <c r="X138" t="inlineStr">
-        <is>
-          <t>麻风病</t>
-        </is>
-      </c>
-      <c r="Y138" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z138" t="inlineStr">
-        <is>
-          <t>provincial_statutory_infectious_disease_monthly_report</t>
-        </is>
-      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB138" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>country:CN-JS:national</t>
-        </is>
-      </c>
-      <c r="AD138" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE138" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF138" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG138" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH138" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI138" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ138" t="inlineStr">
-        <is>
-          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
-        </is>
-      </c>
-      <c r="AK138" t="inlineStr">
-        <is>
-          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
-        </is>
-      </c>
-      <c r="AM138" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN138" t="b">
-        <v>1</v>
       </c>
       <c r="AO138" t="inlineStr">
         <is>
@@ -23024,17 +22935,17 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>CN-LN</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Liaoning, China</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -23073,20 +22984,98 @@
       <c r="O139" t="n">
         <v>0</v>
       </c>
-      <c r="S139" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="U139" t="inlineStr">
         <is>
           <t>SER_CN_PROV_REPORT_LEPROSY</t>
         </is>
       </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_LEPROSY</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X139" t="inlineStr">
+        <is>
+          <t>麻风病</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>country:CN-JS:national</t>
+        </is>
+      </c>
+      <c r="AD139" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE139" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF139" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG139" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH139" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI139" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ139" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK139" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM139" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN139" t="b">
+        <v>1</v>
       </c>
       <c r="AO139" t="inlineStr">
         <is>
@@ -23148,7 +23137,7 @@
       </c>
       <c r="BB139" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC139" t="inlineStr">
@@ -23180,7 +23169,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -23229,98 +23218,20 @@
       <c r="O140" t="n">
         <v>0</v>
       </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U140" t="inlineStr">
         <is>
           <t>SER_CN_PROV_REPORT_LEPROSY</t>
         </is>
       </c>
-      <c r="V140" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_REPORT_LEPROSY</t>
-        </is>
-      </c>
-      <c r="W140" t="inlineStr">
-        <is>
-          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
-        </is>
-      </c>
-      <c r="X140" t="inlineStr">
-        <is>
-          <t>麻风病</t>
-        </is>
-      </c>
-      <c r="Y140" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z140" t="inlineStr">
-        <is>
-          <t>provincial_statutory_infectious_disease_monthly_report</t>
-        </is>
-      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB140" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>country:CN-LN:national</t>
-        </is>
-      </c>
-      <c r="AD140" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE140" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF140" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG140" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH140" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI140" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ140" t="inlineStr">
-        <is>
-          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
-        </is>
-      </c>
-      <c r="AK140" t="inlineStr">
-        <is>
-          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
-        </is>
-      </c>
-      <c r="AM140" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN140" t="b">
-        <v>1</v>
       </c>
       <c r="AO140" t="inlineStr">
         <is>
@@ -23414,17 +23325,17 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>CN-SC</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Sichuan, China</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -23458,14 +23369,39 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O141" t="n">
-        <v>2</v>
-      </c>
-      <c r="S141" t="inlineStr">
-        <is>
-          <t>missing_population</t>
+        <v>0</v>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_LEPROSY</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_LEPROSY</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X141" t="inlineStr">
+        <is>
+          <t>麻风病</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -23473,6 +23409,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>country:CN-LN:national</t>
+        </is>
+      </c>
+      <c r="AD141" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE141" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF141" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG141" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH141" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI141" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ141" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK141" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM141" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN141" t="b">
+        <v>1</v>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -23480,7 +23474,7 @@
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>priority_overlay</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ141" t="inlineStr">
@@ -23490,15 +23484,15 @@
       </c>
       <c r="AS141" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_LEPROSY; SER_CN_PROV_REPORT_LEPROSY</t>
+          <t>SER_CN_PROV_REPORT_LEPROSY</t>
         </is>
       </c>
       <c r="AT141" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV141" t="inlineStr">
@@ -23533,7 +23527,7 @@
       </c>
       <c r="BB141" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC141" t="inlineStr">
@@ -23565,7 +23559,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -23614,98 +23608,15 @@
       <c r="O142" t="n">
         <v>2</v>
       </c>
-      <c r="U142" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_REPORT_LEPROSY</t>
-        </is>
-      </c>
-      <c r="V142" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_REPORT_LEPROSY</t>
-        </is>
-      </c>
-      <c r="W142" t="inlineStr">
-        <is>
-          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
-        </is>
-      </c>
-      <c r="X142" t="inlineStr">
-        <is>
-          <t>麻风病</t>
-        </is>
-      </c>
-      <c r="Y142" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z142" t="inlineStr">
-        <is>
-          <t>provincial_statutory_infectious_disease_monthly_report</t>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB142" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>country:CN-SC:national</t>
-        </is>
-      </c>
-      <c r="AD142" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE142" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF142" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG142" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH142" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI142" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ142" t="inlineStr">
-        <is>
-          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
-        </is>
-      </c>
-      <c r="AK142" t="inlineStr">
-        <is>
-          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
-        </is>
-      </c>
-      <c r="AM142" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN142" t="b">
-        <v>1</v>
       </c>
       <c r="AO142" t="inlineStr">
         <is>
@@ -23799,17 +23710,17 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>CN-SH</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -23843,26 +23754,104 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O143" t="n">
-        <v>0</v>
-      </c>
-      <c r="S143" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
+        <v>2</v>
       </c>
       <c r="U143" t="inlineStr">
         <is>
           <t>SER_CN_PROV_REPORT_LEPROSY</t>
         </is>
       </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_LEPROSY</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X143" t="inlineStr">
+        <is>
+          <t>麻风病</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>country:CN-SC:national</t>
+        </is>
+      </c>
+      <c r="AD143" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE143" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF143" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG143" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH143" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI143" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ143" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK143" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM143" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN143" t="b">
+        <v>1</v>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -23870,7 +23859,7 @@
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ143" t="inlineStr">
@@ -23880,15 +23869,15 @@
       </c>
       <c r="AS143" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_REPORT_LEPROSY</t>
+          <t>SER_CN_PROV_DC_LEPROSY; SER_CN_PROV_REPORT_LEPROSY</t>
         </is>
       </c>
       <c r="AT143" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV143" t="inlineStr">
@@ -23923,7 +23912,7 @@
       </c>
       <c r="BB143" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC143" t="inlineStr">
@@ -23955,7 +23944,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -24004,98 +23993,20 @@
       <c r="O144" t="n">
         <v>0</v>
       </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U144" t="inlineStr">
         <is>
           <t>SER_CN_PROV_REPORT_LEPROSY</t>
         </is>
       </c>
-      <c r="V144" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_REPORT_LEPROSY</t>
-        </is>
-      </c>
-      <c r="W144" t="inlineStr">
-        <is>
-          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
-        </is>
-      </c>
-      <c r="X144" t="inlineStr">
-        <is>
-          <t>麻风病</t>
-        </is>
-      </c>
-      <c r="Y144" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z144" t="inlineStr">
-        <is>
-          <t>provincial_statutory_infectious_disease_monthly_report</t>
-        </is>
-      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB144" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC144" t="inlineStr">
-        <is>
-          <t>country:CN-SH:national</t>
-        </is>
-      </c>
-      <c r="AD144" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE144" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF144" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG144" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH144" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI144" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ144" t="inlineStr">
-        <is>
-          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
-        </is>
-      </c>
-      <c r="AK144" t="inlineStr">
-        <is>
-          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
-        </is>
-      </c>
-      <c r="AM144" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN144" t="b">
-        <v>1</v>
       </c>
       <c r="AO144" t="inlineStr">
         <is>
@@ -24189,17 +24100,17 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -24238,76 +24149,165 @@
       <c r="O145" t="n">
         <v>0</v>
       </c>
-      <c r="R145" t="n">
-        <v>0</v>
-      </c>
-      <c r="S145" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_LEPROSY</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_LEPROSY</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X145" t="inlineStr">
+        <is>
+          <t>麻风病</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>country:CN-SH:national</t>
+        </is>
+      </c>
+      <c r="AD145" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE145" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF145" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG145" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH145" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI145" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ145" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK145" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM145" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN145" t="b">
+        <v>1</v>
       </c>
       <c r="AO145" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR145" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS145" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ145" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS145" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_LEPROSY</t>
+        </is>
+      </c>
       <c r="AT145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA145" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB145" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC145" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -24339,12 +24339,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -24378,13 +24378,13 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R146" t="n">
-        <v>0.001937969923792046</v>
+        <v>0</v>
       </c>
       <c r="S146" t="inlineStr">
         <is>
@@ -24417,42 +24417,42 @@
       </c>
       <c r="AV146" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA146" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB146" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC146" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -24484,12 +24484,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -24523,13 +24523,13 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O147" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R147" t="n">
-        <v>0.0008595114398308156</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S147" t="inlineStr">
         <is>
@@ -24562,42 +24562,42 @@
       </c>
       <c r="AV147" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA147" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB147" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC147" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -24659,7 +24659,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -24774,12 +24774,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -24804,22 +24804,22 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N149" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O149" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R149" t="n">
-        <v>0</v>
+        <v>0.0008595114398308156</v>
       </c>
       <c r="S149" t="inlineStr">
         <is>
@@ -24852,42 +24852,42 @@
       </c>
       <c r="AV149" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA149" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB149" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC149" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -24919,12 +24919,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -24958,13 +24958,13 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O150" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R150" t="n">
-        <v>0.003875939847584092</v>
+        <v>0</v>
       </c>
       <c r="S150" t="inlineStr">
         <is>
@@ -24997,42 +24997,42 @@
       </c>
       <c r="AV150" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA150" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB150" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC150" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -25064,12 +25064,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -25094,7 +25094,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -25103,13 +25103,13 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="O151" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="R151" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0.008896686069425903</v>
       </c>
       <c r="S151" t="inlineStr">
         <is>
@@ -25142,42 +25142,622 @@
       </c>
       <c r="AV151" t="inlineStr">
         <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX151" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA151" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB151" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC151" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>leprosy</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>麻风病</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N152" t="n">
+        <v>2</v>
+      </c>
+      <c r="O152" t="n">
+        <v>2</v>
+      </c>
+      <c r="R152" t="n">
+        <v>0.003875939847584092</v>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO152" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP152" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR152" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS152" t="inlineStr"/>
+      <c r="AT152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU152" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV152" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW152" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX152" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA152" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB152" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC152" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>leprosy</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>麻风病</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N153" t="n">
+        <v>1</v>
+      </c>
+      <c r="O153" t="n">
+        <v>1</v>
+      </c>
+      <c r="R153" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO153" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP153" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR153" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS153" t="inlineStr"/>
+      <c r="AT153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU153" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV153" t="inlineStr">
+        <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW151" t="inlineStr">
+      <c r="AW153" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX151" t="inlineStr">
+      <c r="AX153" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY151" t="inlineStr">
+      <c r="AY153" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ151" t="inlineStr">
+      <c r="AZ153" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA151" t="inlineStr">
+      <c r="BA153" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB151" t="inlineStr">
+      <c r="BB153" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC151" t="inlineStr">
+      <c r="BC153" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>leprosy</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>麻风病</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N154" t="n">
+        <v>1</v>
+      </c>
+      <c r="O154" t="n">
+        <v>1</v>
+      </c>
+      <c r="R154" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO154" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP154" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR154" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS154" t="inlineStr"/>
+      <c r="AT154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU154" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV154" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW154" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX154" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY154" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA154" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB154" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC154" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>leprosy</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>麻风病</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N155" t="n">
+        <v>0</v>
+      </c>
+      <c r="O155" t="n">
+        <v>0</v>
+      </c>
+      <c r="R155" t="n">
+        <v>0</v>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO155" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP155" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR155" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS155" t="inlineStr"/>
+      <c r="AT155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU155" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV155" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA155" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB155" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC155" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -25214,7 +25794,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -25297,7 +25877,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10">
@@ -25307,7 +25887,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11">
@@ -25359,7 +25939,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3532</v>
+        <v>5052</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d042/2026-2029.xlsx
+++ b/diseases/d042/2026-2029.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -921,6 +926,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1057,6 +1067,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1202,6 +1217,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1347,6 +1367,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1492,6 +1517,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1637,6 +1667,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1782,6 +1817,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1927,6 +1967,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2075,6 +2120,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2220,6 +2270,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2356,6 +2411,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2492,6 +2552,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2628,6 +2693,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2764,6 +2834,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2900,6 +2975,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3036,6 +3116,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3172,6 +3257,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3308,6 +3398,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3444,6 +3539,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3580,6 +3680,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3716,6 +3821,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3852,6 +3962,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3988,6 +4103,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4124,6 +4244,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4260,6 +4385,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4396,6 +4526,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4532,6 +4667,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4668,6 +4808,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4804,6 +4949,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4940,6 +5090,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5076,6 +5231,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5212,6 +5372,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5348,6 +5513,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5484,6 +5654,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5620,6 +5795,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5756,6 +5936,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5895,6 +6080,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6425,6 +6615,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6570,6 +6765,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6718,6 +6918,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6866,6 +7071,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7014,6 +7224,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7162,6 +7377,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7310,6 +7530,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7458,6 +7683,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7603,6 +7833,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7739,6 +7974,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7875,6 +8115,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8020,6 +8265,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8165,6 +8415,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8310,6 +8565,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8455,6 +8715,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8600,6 +8865,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8748,6 +9018,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8893,6 +9168,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9029,6 +9309,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9165,6 +9450,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9301,6 +9591,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9437,6 +9732,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9573,6 +9873,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9709,6 +10014,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9845,6 +10155,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9981,6 +10296,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10117,6 +10437,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10253,6 +10578,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10389,6 +10719,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10525,6 +10860,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10661,6 +11001,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10797,6 +11142,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10933,6 +11283,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11069,6 +11424,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11205,6 +11565,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11341,6 +11706,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11477,6 +11847,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11613,6 +11988,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11749,6 +12129,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11885,6 +12270,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12021,6 +12411,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12157,6 +12552,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12293,6 +12693,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12429,6 +12834,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12568,6 +12978,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13098,6 +13513,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13243,6 +13663,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13391,6 +13816,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13539,6 +13969,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13687,6 +14122,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13835,6 +14275,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13983,6 +14428,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14128,6 +14578,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14264,6 +14719,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14409,6 +14869,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14545,6 +15010,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14690,6 +15160,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14835,6 +15310,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14980,6 +15460,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15125,6 +15610,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15270,6 +15760,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15406,6 +15901,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15542,6 +16042,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15678,6 +16183,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO107" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15814,6 +16324,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15950,6 +16465,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16086,6 +16606,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16222,6 +16747,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16358,6 +16888,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16494,6 +17029,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16630,6 +17170,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16766,6 +17311,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16902,6 +17452,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17038,6 +17593,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17174,6 +17734,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO118" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17310,6 +17875,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17446,6 +18016,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17582,6 +18157,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17718,6 +18298,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17854,6 +18439,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17990,6 +18580,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18126,6 +18721,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18262,6 +18862,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO126" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18398,6 +19003,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18534,6 +19144,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18670,6 +19285,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18806,6 +19426,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18945,6 +19570,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19090,6 +19720,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19235,6 +19870,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO133" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19383,6 +20023,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO134" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19531,6 +20176,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19679,6 +20329,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19827,6 +20482,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19972,6 +20632,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO138" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20117,6 +20782,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO139" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20262,6 +20932,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20407,6 +21082,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20552,6 +21232,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO142" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20697,6 +21382,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20842,6 +21532,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO144" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20987,6 +21682,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21123,6 +21823,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO146" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21268,6 +21973,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO147" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21404,6 +22114,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21540,6 +22255,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO149" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21676,6 +22396,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO150" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21812,6 +22537,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO151" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21948,6 +22678,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO152" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22084,6 +22819,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO153" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22220,6 +22960,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO154" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22356,6 +23101,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO155" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22492,6 +23242,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO156" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22628,6 +23383,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO157" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22764,6 +23524,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO158" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22900,6 +23665,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO159" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23036,6 +23806,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO160" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23172,6 +23947,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO161" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23308,6 +24088,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO162" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23444,6 +24229,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO163" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23580,6 +24370,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO164" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23716,6 +24511,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO165" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23852,6 +24652,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO166" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23988,6 +24793,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO167" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24124,6 +24934,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO168" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24260,6 +25075,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO169" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24396,6 +25216,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO170" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24532,6 +25357,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO171" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24668,6 +25498,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO172" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24804,6 +25639,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO173" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24943,6 +25783,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO174" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25088,6 +25933,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO175" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25233,6 +26083,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO176" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25381,6 +26236,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO177" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25529,6 +26389,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO178" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25677,6 +26542,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO179" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25825,6 +26695,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO180" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25970,6 +26845,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO181" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26115,6 +26995,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO182" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26260,6 +27145,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO183" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26405,6 +27295,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO184" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26550,6 +27445,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO185" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26695,6 +27595,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO186" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26840,6 +27745,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO187" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26985,6 +27895,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO188" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27130,6 +28045,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO189" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27275,6 +28195,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO190" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27420,6 +28345,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO191" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27556,6 +28486,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO192" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27692,6 +28627,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO193" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27828,6 +28768,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO194" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27964,6 +28909,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO195" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28100,6 +29050,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO196" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28236,6 +29191,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO197" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28372,6 +29332,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO198" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28508,6 +29473,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO199" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28644,6 +29614,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO200" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28780,6 +29755,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO201" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28916,6 +29896,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO202" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29052,6 +30037,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO203" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29188,6 +30178,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO204" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29324,6 +30319,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO205" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29460,6 +30460,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO206" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29596,6 +30601,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO207" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29732,6 +30742,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO208" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29868,6 +30883,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO209" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30004,6 +31024,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO210" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30140,6 +31165,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO211" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30276,6 +31306,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO212" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30412,6 +31447,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO213" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30548,6 +31588,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO214" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30684,6 +31729,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO215" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30820,6 +31870,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO216" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30956,6 +32011,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO217" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31095,6 +32155,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO218" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32010,6 +33075,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO223" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32155,6 +33225,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO224" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32303,6 +33378,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO225" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32451,6 +33531,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO226" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32599,6 +33684,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO227" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32747,6 +33837,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO228" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32892,6 +33987,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO229" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33037,6 +34137,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO230" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33182,6 +34287,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO231" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33318,6 +34428,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO232" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33463,6 +34578,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO233" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33608,6 +34728,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO234" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33753,6 +34878,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO235" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33898,6 +35028,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO236" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34043,6 +35178,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO237" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34188,6 +35328,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO238" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34333,6 +35478,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO239" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34469,6 +35619,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO240" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34605,6 +35760,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA241" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO241" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34741,6 +35901,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO242" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34877,6 +36042,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO243" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35013,6 +36183,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO244" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35149,6 +36324,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO245" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35285,6 +36465,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO246" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35421,6 +36606,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO247" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35557,6 +36747,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO248" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35693,6 +36888,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO249" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35829,6 +37029,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO250" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35965,6 +37170,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO251" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36101,6 +37311,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO252" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36237,6 +37452,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA253" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO253" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36373,6 +37593,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA254" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO254" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36509,6 +37734,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO255" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36645,6 +37875,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO256" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36781,6 +38016,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA257" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO257" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36917,6 +38157,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO258" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37053,6 +38298,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA259" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO259" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37189,6 +38439,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA260" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO260" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37325,6 +38580,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO261" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37461,6 +38721,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA262" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO262" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37597,6 +38862,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA263" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO263" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37733,6 +39003,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA264" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO264" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37869,6 +39144,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA265" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO265" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38008,6 +39288,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA266" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO266" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41248,6 +42533,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA283" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO283" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41393,6 +42683,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA284" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO284" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41538,6 +42833,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA285" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO285" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41683,6 +42983,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA286" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO286" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41828,6 +43133,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA287" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO287" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41973,6 +43283,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA288" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO288" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42118,6 +43433,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA289" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO289" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42263,6 +43583,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA290" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO290" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42408,6 +43733,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA291" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO291" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42553,6 +43883,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA292" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO292" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42698,6 +44033,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA293" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO293" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42843,6 +44183,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA294" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO294" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42988,6 +44333,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA295" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO295" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43133,6 +44483,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA296" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO296" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43278,6 +44633,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA297" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO297" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43423,6 +44783,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA298" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO298" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43559,6 +44924,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA299" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO299" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43695,6 +45065,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA300" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO300" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43831,6 +45206,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA301" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO301" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43967,6 +45347,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA302" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO302" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44103,6 +45488,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA303" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO303" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44239,6 +45629,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA304" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO304" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44375,6 +45770,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA305" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO305" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44511,6 +45911,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA306" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO306" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44647,6 +46052,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA307" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO307" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44783,6 +46193,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA308" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO308" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44919,6 +46334,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA309" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO309" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45055,6 +46475,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA310" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO310" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45191,6 +46616,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA311" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO311" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45327,6 +46757,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA312" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO312" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45463,6 +46898,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA313" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO313" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45599,6 +47039,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA314" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO314" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45735,6 +47180,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA315" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO315" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45871,6 +47321,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA316" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO316" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46007,6 +47462,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA317" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO317" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46143,6 +47603,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA318" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO318" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46279,6 +47744,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA319" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO319" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46415,6 +47885,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA320" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO320" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46551,6 +48026,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA321" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO321" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46687,6 +48167,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA322" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO322" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46823,6 +48308,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA323" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO323" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46959,6 +48449,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA324" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO324" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47098,6 +48593,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA325" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO325" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50723,6 +52223,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA344" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO344" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50868,6 +52373,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA345" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO345" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51158,6 +52668,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA347" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO347" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51303,6 +52818,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA348" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO348" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51448,6 +52968,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA349" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO349" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51593,6 +53118,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA350" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO350" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51738,6 +53268,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA351" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO351" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51883,6 +53418,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA352" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO352" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52028,6 +53568,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA353" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO353" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52173,6 +53718,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA354" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO354" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52318,6 +53868,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA355" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO355" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52463,6 +54018,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA356" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO356" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52608,6 +54168,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA357" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO357" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52753,6 +54318,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA358" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO358" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52898,6 +54468,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA359" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO359" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53043,6 +54618,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA360" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO360" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53188,6 +54768,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA361" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO361" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53324,6 +54909,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA362" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO362" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53460,6 +55050,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA363" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO363" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53596,6 +55191,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA364" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO364" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53732,6 +55332,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA365" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO365" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53868,6 +55473,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA366" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO366" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54004,6 +55614,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA367" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO367" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54140,6 +55755,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA368" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO368" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54276,6 +55896,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA369" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO369" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54412,6 +56037,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA370" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO370" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54548,6 +56178,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA371" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO371" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54684,6 +56319,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA372" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO372" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54820,6 +56460,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA373" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO373" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54956,6 +56601,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA374" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO374" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55092,6 +56742,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA375" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO375" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55228,6 +56883,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA376" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO376" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55364,6 +57024,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA377" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO377" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55500,6 +57165,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA378" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO378" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55636,6 +57306,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA379" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO379" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55772,6 +57447,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA380" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO380" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55908,6 +57588,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA381" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO381" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56044,6 +57729,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA382" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO382" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56180,6 +57870,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA383" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO383" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56316,6 +58011,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA384" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO384" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56452,6 +58152,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA385" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO385" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56588,6 +58293,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA386" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO386" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56724,6 +58434,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA387" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO387" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56863,6 +58578,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA388" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO388" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59718,6 +61438,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA403" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO403" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59863,6 +61588,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA404" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO404" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60008,6 +61738,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA405" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO405" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60153,6 +61888,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA406" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO406" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60285,17 +62025,22 @@
         </is>
       </c>
       <c r="N407" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O407" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R407" t="n">
-        <v>0</v>
+        <v>0.00367281181951979</v>
       </c>
       <c r="S407" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA407" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO407" t="inlineStr">
@@ -60443,6 +62188,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA408" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO408" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60588,6 +62338,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA409" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO409" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60733,6 +62488,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA410" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO410" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60878,6 +62638,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA411" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO411" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61023,6 +62788,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA412" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO412" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61168,6 +62938,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA413" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO413" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61313,6 +63088,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA414" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO414" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61458,6 +63238,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA415" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO415" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61603,6 +63388,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA416" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO416" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61748,6 +63538,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA417" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO417" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61884,6 +63679,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA418" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO418" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -62020,6 +63820,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA419" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO419" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -62156,6 +63961,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA420" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO420" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -62292,6 +64102,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA421" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO421" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -62428,6 +64243,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA422" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO422" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -62564,6 +64384,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA423" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO423" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -62700,6 +64525,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA424" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO424" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -62836,6 +64666,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA425" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO425" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -62972,6 +64807,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA426" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO426" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63108,6 +64948,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA427" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO427" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63244,6 +65089,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA428" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO428" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63380,6 +65230,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA429" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO429" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63516,6 +65371,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA430" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO430" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63652,6 +65512,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA431" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO431" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63788,6 +65653,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA432" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO432" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63924,6 +65794,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA433" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO433" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64060,6 +65935,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA434" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO434" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64196,6 +66076,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA435" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO435" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64332,6 +66217,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA436" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO436" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64468,6 +66358,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA437" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO437" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64604,6 +66499,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA438" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO438" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64740,6 +66640,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA439" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO439" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64876,6 +66781,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA440" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO440" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65012,6 +66922,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA441" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO441" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65148,6 +67063,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA442" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO442" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65284,6 +67204,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA443" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO443" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65420,6 +67345,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA444" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO444" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65565,6 +67495,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA445" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO445" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65710,6 +67645,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA446" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO446" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65855,6 +67795,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA447" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO447" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65917,6 +67862,156 @@
       <c r="BC447" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>leprosy</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="J448" t="inlineStr">
+        <is>
+          <t>麻风病</t>
+        </is>
+      </c>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L448" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="M448" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N448" t="n">
+        <v>1</v>
+      </c>
+      <c r="O448" t="n">
+        <v>1</v>
+      </c>
+      <c r="R448" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S448" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA448" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO448" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP448" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR448" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS448" t="inlineStr"/>
+      <c r="AT448" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU448" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV448" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW448" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX448" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY448" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ448" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA448" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB448" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC448" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -65953,7 +68048,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -66036,7 +68131,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="10">
@@ -66046,7 +68141,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="11">
@@ -66098,7 +68193,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>23892</v>
+        <v>23894</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d042/2026-2029.xlsx
+++ b/diseases/d042/2026-2029.xlsx
@@ -6907,9 +6907,6 @@
       <c r="O44" t="n">
         <v>1</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -7213,9 +7210,6 @@
       <c r="O46" t="n">
         <v>2</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0.0005730076265538771</v>
       </c>
@@ -13958,9 +13952,6 @@
       <c r="O92" t="n">
         <v>4</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0.001146015253107754</v>
       </c>
@@ -14111,9 +14102,6 @@
       <c r="O93" t="n">
         <v>1</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -14264,9 +14252,6 @@
       <c r="O94" t="n">
         <v>1</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -20318,9 +20303,6 @@
       <c r="O136" t="n">
         <v>1</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -20471,9 +20453,6 @@
       <c r="O137" t="n">
         <v>1</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -26378,9 +26357,6 @@
       <c r="O178" t="n">
         <v>2</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>0.0005730076265538771</v>
       </c>
@@ -26531,9 +26507,6 @@
       <c r="O179" t="n">
         <v>3</v>
       </c>
-      <c r="Q179" t="n">
-        <v>0</v>
-      </c>
       <c r="R179" t="n">
         <v>0.0008595114398308156</v>
       </c>
@@ -33367,9 +33340,6 @@
       <c r="O225" t="n">
         <v>3</v>
       </c>
-      <c r="Q225" t="n">
-        <v>0</v>
-      </c>
       <c r="R225" t="n">
         <v>0.0008595114398308156</v>
       </c>
@@ -33673,9 +33643,6 @@
       <c r="O227" t="n">
         <v>1</v>
       </c>
-      <c r="Q227" t="n">
-        <v>0</v>
-      </c>
       <c r="R227" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -33821,16 +33788,13 @@
         </is>
       </c>
       <c r="N228" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O228" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q228" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R228" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S228" t="inlineStr">
         <is>
@@ -68010,6 +67974,156 @@
         </is>
       </c>
       <c r="BC448" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>leprosy</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="J449" t="inlineStr">
+        <is>
+          <t>麻风病</t>
+        </is>
+      </c>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M449" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N449" t="n">
+        <v>1</v>
+      </c>
+      <c r="O449" t="n">
+        <v>1</v>
+      </c>
+      <c r="R449" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S449" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA449" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO449" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP449" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR449" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS449" t="inlineStr"/>
+      <c r="AT449" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU449" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV449" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW449" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX449" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY449" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ449" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA449" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB449" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC449" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -68048,7 +68162,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -68131,7 +68245,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="10">
@@ -68141,7 +68255,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d042/2026-2029.xlsx
+++ b/diseases/d042/2026-2029.xlsx
@@ -62944,12 +62944,12 @@
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H472" t="inlineStr">
@@ -63012,42 +63012,42 @@
       </c>
       <c r="AV472" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW472" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX472" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY472" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ472" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA472" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB472" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC472" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -63079,12 +63079,12 @@
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H473" t="inlineStr">
@@ -63109,7 +63109,7 @@
       </c>
       <c r="L473" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="M473" t="inlineStr">
@@ -63118,30 +63118,22 @@
         </is>
       </c>
       <c r="N473" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O473" t="n">
-        <v>1</v>
-      </c>
-      <c r="P473" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R473" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="U473" t="inlineStr">
-        <is>
-          <t>HOLD_US_23efe3522b8141a771af70d76b4d</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AA473" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO473" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP473" t="inlineStr">
@@ -63149,52 +63141,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS473" t="inlineStr">
-        <is>
-          <t>HOLD_US_23efe3522b8141a771af70d76b4d</t>
-        </is>
-      </c>
+      <c r="AS473" t="inlineStr"/>
       <c r="AT473" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV473" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW473" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX473" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY473" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ473" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA473" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB473" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC473" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -63226,12 +63214,12 @@
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>US-FL</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>Florida, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H474" t="inlineStr">
@@ -63273,6 +63261,9 @@
       <c r="P474" t="n">
         <v>1</v>
       </c>
+      <c r="R474" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
       <c r="U474" t="inlineStr">
         <is>
           <t>HOLD_US_23efe3522b8141a771af70d76b4d</t>
@@ -63285,7 +63276,7 @@
       </c>
       <c r="AO474" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP474" t="inlineStr">
@@ -63313,32 +63304,32 @@
       </c>
       <c r="AX474" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY474" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ474" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA474" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB474" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC474" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -63370,12 +63361,12 @@
       </c>
       <c r="F475" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>US-FL</t>
         </is>
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Florida, United States</t>
         </is>
       </c>
       <c r="H475" t="inlineStr">
@@ -63400,7 +63391,7 @@
       </c>
       <c r="L475" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="M475" t="inlineStr">
@@ -63417,9 +63408,6 @@
       <c r="P475" t="n">
         <v>1</v>
       </c>
-      <c r="R475" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
       <c r="U475" t="inlineStr">
         <is>
           <t>HOLD_US_23efe3522b8141a771af70d76b4d</t>
@@ -63432,7 +63420,7 @@
       </c>
       <c r="AO475" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP475" t="inlineStr">
@@ -63460,32 +63448,32 @@
       </c>
       <c r="AX475" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY475" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ475" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA475" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB475" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC475" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -63517,12 +63505,12 @@
       </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>US-FL</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>Florida, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H476" t="inlineStr">
@@ -63564,6 +63552,9 @@
       <c r="P476" t="n">
         <v>1</v>
       </c>
+      <c r="R476" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
       <c r="U476" t="inlineStr">
         <is>
           <t>HOLD_US_23efe3522b8141a771af70d76b4d</t>
@@ -63576,7 +63567,7 @@
       </c>
       <c r="AO476" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP476" t="inlineStr">
@@ -63604,30 +63595,174 @@
       </c>
       <c r="AX476" t="inlineStr">
         <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY476" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ476" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA476" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB476" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC476" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>leprosy</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>US-FL</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>Florida, United States</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="J477" t="inlineStr">
+        <is>
+          <t>麻风病</t>
+        </is>
+      </c>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L477" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M477" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N477" t="n">
+        <v>1</v>
+      </c>
+      <c r="O477" t="n">
+        <v>1</v>
+      </c>
+      <c r="P477" t="n">
+        <v>1</v>
+      </c>
+      <c r="U477" t="inlineStr">
+        <is>
+          <t>HOLD_US_23efe3522b8141a771af70d76b4d</t>
+        </is>
+      </c>
+      <c r="AA477" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO477" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP477" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS477" t="inlineStr">
+        <is>
+          <t>HOLD_US_23efe3522b8141a771af70d76b4d</t>
+        </is>
+      </c>
+      <c r="AT477" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV477" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW477" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX477" t="inlineStr">
+        <is>
           <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
-      <c r="AY476" t="inlineStr">
+      <c r="AY477" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ476" t="inlineStr">
+      <c r="AZ477" t="inlineStr">
         <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="BA476" t="inlineStr">
+      <c r="BA477" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="BB476" t="inlineStr">
+      <c r="BB477" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
-      <c r="BC476" t="inlineStr">
+      <c r="BC477" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -63749,7 +63884,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="10">
@@ -63759,7 +63894,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d042/2026-2029.xlsx
+++ b/diseases/d042/2026-2029.xlsx
@@ -771,6 +771,11 @@
       <c r="R2" t="n">
         <v>0</v>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -783,12 +788,22 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -906,6 +921,11 @@
       <c r="R3" t="n">
         <v>0</v>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -918,12 +938,22 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1032,6 +1062,11 @@
           <t>2026-01</t>
         </is>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1044,12 +1079,22 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1167,6 +1212,11 @@
       <c r="R5" t="n">
         <v>0</v>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1179,12 +1229,22 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1302,6 +1362,11 @@
       <c r="R6" t="n">
         <v>0</v>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1314,12 +1379,22 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1437,6 +1512,11 @@
       <c r="R7" t="n">
         <v>0</v>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1449,12 +1529,22 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1572,6 +1662,11 @@
       <c r="R8" t="n">
         <v>0</v>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1584,12 +1679,22 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1707,6 +1812,11 @@
       <c r="R9" t="n">
         <v>0</v>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1719,12 +1829,22 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -1842,6 +1962,11 @@
       <c r="R10" t="n">
         <v>0</v>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1854,12 +1979,22 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -6078,6 +6213,11 @@
       <c r="R43" t="n">
         <v>0</v>
       </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6090,12 +6230,22 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -6213,6 +6363,11 @@
       <c r="R44" t="n">
         <v>0</v>
       </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6225,12 +6380,22 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
@@ -7527,6 +7692,11 @@
       <c r="R53" t="n">
         <v>0</v>
       </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7539,12 +7709,22 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
         <v>0</v>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
@@ -7662,6 +7842,11 @@
       <c r="R54" t="n">
         <v>0</v>
       </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7674,12 +7859,22 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
         <v>0</v>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
@@ -7788,6 +7983,11 @@
           <t>2026-02</t>
         </is>
       </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7800,12 +8000,22 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="n">
         <v>0</v>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
@@ -7914,6 +8124,11 @@
           <t>2026-02</t>
         </is>
       </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7926,12 +8141,22 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
         <v>0</v>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
@@ -8049,6 +8274,11 @@
       <c r="R57" t="n">
         <v>0</v>
       </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8061,12 +8291,22 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
@@ -8184,6 +8424,11 @@
       <c r="R58" t="n">
         <v>0</v>
       </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8196,12 +8441,22 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
@@ -8319,6 +8574,11 @@
       <c r="R59" t="n">
         <v>0</v>
       </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8331,12 +8591,22 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR59" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
         <v>0</v>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
@@ -8454,6 +8724,11 @@
       <c r="R60" t="n">
         <v>0</v>
       </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8466,12 +8741,22 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="n">
         <v>0</v>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
@@ -8589,6 +8874,11 @@
       <c r="R61" t="n">
         <v>0</v>
       </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8601,12 +8891,22 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR61" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="n">
         <v>0</v>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
@@ -12825,6 +13125,11 @@
       <c r="R94" t="n">
         <v>0</v>
       </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12837,12 +13142,22 @@
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR94" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="n">
         <v>0</v>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
@@ -12960,6 +13275,11 @@
       <c r="R95" t="n">
         <v>0</v>
       </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12972,12 +13292,22 @@
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR95" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="n">
         <v>0</v>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
@@ -14744,6 +15074,11 @@
       <c r="R106" t="n">
         <v>0</v>
       </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14756,12 +15091,22 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr"/>
       <c r="AT106" t="n">
         <v>0</v>
+      </c>
+      <c r="AU106" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
@@ -14879,6 +15224,11 @@
       <c r="R107" t="n">
         <v>0</v>
       </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14891,12 +15241,22 @@
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR107" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS107" t="inlineStr"/>
       <c r="AT107" t="n">
         <v>0</v>
+      </c>
+      <c r="AU107" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
@@ -15005,6 +15365,11 @@
           <t>2026-03</t>
         </is>
       </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15017,12 +15382,22 @@
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR108" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS108" t="inlineStr"/>
       <c r="AT108" t="n">
         <v>0</v>
+      </c>
+      <c r="AU108" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
@@ -15140,6 +15515,11 @@
       <c r="R109" t="n">
         <v>0</v>
       </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15152,12 +15532,22 @@
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR109" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS109" t="inlineStr"/>
       <c r="AT109" t="n">
         <v>0</v>
+      </c>
+      <c r="AU109" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
@@ -15266,6 +15656,11 @@
           <t>2026-03</t>
         </is>
       </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15278,12 +15673,22 @@
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR110" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS110" t="inlineStr"/>
       <c r="AT110" t="n">
         <v>0</v>
+      </c>
+      <c r="AU110" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
@@ -15401,6 +15806,11 @@
       <c r="R111" t="n">
         <v>0</v>
       </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15413,12 +15823,22 @@
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR111" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS111" t="inlineStr"/>
       <c r="AT111" t="n">
         <v>0</v>
+      </c>
+      <c r="AU111" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
@@ -15536,6 +15956,11 @@
       <c r="R112" t="n">
         <v>0</v>
       </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15548,12 +15973,22 @@
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR112" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr"/>
       <c r="AT112" t="n">
         <v>0</v>
+      </c>
+      <c r="AU112" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
@@ -15671,6 +16106,11 @@
       <c r="R113" t="n">
         <v>0</v>
       </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15683,12 +16123,22 @@
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR113" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS113" t="inlineStr"/>
       <c r="AT113" t="n">
         <v>0</v>
+      </c>
+      <c r="AU113" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
@@ -15806,6 +16256,11 @@
       <c r="R114" t="n">
         <v>0</v>
       </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15818,12 +16273,22 @@
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR114" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS114" t="inlineStr"/>
       <c r="AT114" t="n">
         <v>0</v>
+      </c>
+      <c r="AU114" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
@@ -19763,6 +20228,11 @@
       <c r="R145" t="n">
         <v>0.01355270280196709</v>
       </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19775,12 +20245,22 @@
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR145" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS145" t="inlineStr"/>
       <c r="AT145" t="n">
         <v>0</v>
+      </c>
+      <c r="AU145" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
@@ -19898,6 +20378,11 @@
       <c r="R146" t="n">
         <v>0</v>
       </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19910,12 +20395,22 @@
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR146" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS146" t="inlineStr"/>
       <c r="AT146" t="n">
         <v>0</v>
+      </c>
+      <c r="AU146" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV146" t="inlineStr">
         <is>
@@ -20771,6 +21266,11 @@
       <c r="R152" t="n">
         <v>0</v>
       </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20783,12 +21283,22 @@
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR152" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS152" t="inlineStr"/>
       <c r="AT152" t="n">
         <v>0</v>
+      </c>
+      <c r="AU152" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
@@ -20906,6 +21416,11 @@
       <c r="R153" t="n">
         <v>0</v>
       </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20918,12 +21433,22 @@
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR153" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS153" t="inlineStr"/>
       <c r="AT153" t="n">
         <v>0</v>
+      </c>
+      <c r="AU153" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV153" t="inlineStr">
         <is>
@@ -21041,6 +21566,11 @@
       <c r="R154" t="n">
         <v>0</v>
       </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21053,12 +21583,22 @@
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR154" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS154" t="inlineStr"/>
       <c r="AT154" t="n">
         <v>0</v>
+      </c>
+      <c r="AU154" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV154" t="inlineStr">
         <is>
@@ -21176,6 +21716,11 @@
       <c r="R155" t="n">
         <v>0</v>
       </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21188,12 +21733,22 @@
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR155" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS155" t="inlineStr"/>
       <c r="AT155" t="n">
         <v>0</v>
+      </c>
+      <c r="AU155" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
@@ -21311,6 +21866,11 @@
       <c r="R156" t="n">
         <v>0</v>
       </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21323,12 +21883,22 @@
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR156" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS156" t="inlineStr"/>
       <c r="AT156" t="n">
         <v>0</v>
+      </c>
+      <c r="AU156" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
@@ -21446,6 +22016,11 @@
       <c r="R157" t="n">
         <v>0</v>
       </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21458,12 +22033,22 @@
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR157" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS157" t="inlineStr"/>
       <c r="AT157" t="n">
         <v>0</v>
+      </c>
+      <c r="AU157" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
@@ -21581,6 +22166,11 @@
       <c r="R158" t="n">
         <v>0</v>
       </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21593,12 +22183,22 @@
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR158" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS158" t="inlineStr"/>
       <c r="AT158" t="n">
         <v>0</v>
+      </c>
+      <c r="AU158" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV158" t="inlineStr">
         <is>
@@ -21716,6 +22316,11 @@
       <c r="R159" t="n">
         <v>0</v>
       </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21728,12 +22333,22 @@
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR159" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS159" t="inlineStr"/>
       <c r="AT159" t="n">
         <v>0</v>
+      </c>
+      <c r="AU159" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV159" t="inlineStr">
         <is>
@@ -21842,6 +22457,11 @@
           <t>2026-04</t>
         </is>
       </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21854,12 +22474,22 @@
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR160" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS160" t="inlineStr"/>
       <c r="AT160" t="n">
         <v>0</v>
+      </c>
+      <c r="AU160" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV160" t="inlineStr">
         <is>
@@ -25940,6 +26570,11 @@
       <c r="R192" t="n">
         <v>0</v>
       </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA192" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25952,12 +26587,22 @@
       </c>
       <c r="AP192" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR192" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS192" t="inlineStr"/>
       <c r="AT192" t="n">
         <v>0</v>
+      </c>
+      <c r="AU192" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV192" t="inlineStr">
         <is>
@@ -26075,6 +26720,11 @@
       <c r="R193" t="n">
         <v>0</v>
       </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA193" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26087,12 +26737,22 @@
       </c>
       <c r="AP193" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR193" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS193" t="inlineStr"/>
       <c r="AT193" t="n">
         <v>0</v>
+      </c>
+      <c r="AU193" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV193" t="inlineStr">
         <is>
@@ -27236,6 +27896,11 @@
       <c r="R201" t="n">
         <v>0</v>
       </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA201" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27248,12 +27913,22 @@
       </c>
       <c r="AP201" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR201" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS201" t="inlineStr"/>
       <c r="AT201" t="n">
         <v>0</v>
+      </c>
+      <c r="AU201" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV201" t="inlineStr">
         <is>
@@ -27371,6 +28046,11 @@
       <c r="R202" t="n">
         <v>0</v>
       </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA202" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27383,12 +28063,22 @@
       </c>
       <c r="AP202" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR202" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS202" t="inlineStr"/>
       <c r="AT202" t="n">
         <v>0</v>
+      </c>
+      <c r="AU202" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV202" t="inlineStr">
         <is>
@@ -27506,6 +28196,11 @@
       <c r="R203" t="n">
         <v>0</v>
       </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA203" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27518,12 +28213,22 @@
       </c>
       <c r="AP203" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR203" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS203" t="inlineStr"/>
       <c r="AT203" t="n">
         <v>0</v>
+      </c>
+      <c r="AU203" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV203" t="inlineStr">
         <is>
@@ -27641,6 +28346,11 @@
       <c r="R204" t="n">
         <v>0</v>
       </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA204" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27653,12 +28363,22 @@
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR204" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS204" t="inlineStr"/>
       <c r="AT204" t="n">
         <v>0</v>
+      </c>
+      <c r="AU204" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV204" t="inlineStr">
         <is>
@@ -27776,6 +28496,11 @@
       <c r="R205" t="n">
         <v>0</v>
       </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA205" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27788,12 +28513,22 @@
       </c>
       <c r="AP205" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR205" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS205" t="inlineStr"/>
       <c r="AT205" t="n">
         <v>0</v>
+      </c>
+      <c r="AU205" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV205" t="inlineStr">
         <is>
@@ -27911,6 +28646,11 @@
       <c r="R206" t="n">
         <v>0</v>
       </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA206" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27923,12 +28663,22 @@
       </c>
       <c r="AP206" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR206" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS206" t="inlineStr"/>
       <c r="AT206" t="n">
         <v>0</v>
+      </c>
+      <c r="AU206" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV206" t="inlineStr">
         <is>
@@ -28046,6 +28796,11 @@
       <c r="R207" t="n">
         <v>0</v>
       </c>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA207" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28058,12 +28813,22 @@
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR207" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS207" t="inlineStr"/>
       <c r="AT207" t="n">
         <v>0</v>
+      </c>
+      <c r="AU207" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV207" t="inlineStr">
         <is>
@@ -28181,6 +28946,11 @@
       <c r="R208" t="n">
         <v>0</v>
       </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA208" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28193,12 +28963,22 @@
       </c>
       <c r="AP208" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR208" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS208" t="inlineStr"/>
       <c r="AT208" t="n">
         <v>0</v>
+      </c>
+      <c r="AU208" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV208" t="inlineStr">
         <is>
@@ -28316,6 +29096,11 @@
       <c r="R209" t="n">
         <v>0</v>
       </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA209" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28328,12 +29113,22 @@
       </c>
       <c r="AP209" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR209" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS209" t="inlineStr"/>
       <c r="AT209" t="n">
         <v>0</v>
+      </c>
+      <c r="AU209" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV209" t="inlineStr">
         <is>
@@ -33113,6 +33908,11 @@
       <c r="R246" t="n">
         <v>0</v>
       </c>
+      <c r="S246" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA246" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -33125,12 +33925,22 @@
       </c>
       <c r="AP246" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR246" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS246" t="inlineStr"/>
       <c r="AT246" t="n">
         <v>0</v>
+      </c>
+      <c r="AU246" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV246" t="inlineStr">
         <is>
@@ -33248,6 +34058,11 @@
       <c r="R247" t="n">
         <v>0</v>
       </c>
+      <c r="S247" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA247" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -33260,12 +34075,22 @@
       </c>
       <c r="AP247" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR247" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS247" t="inlineStr"/>
       <c r="AT247" t="n">
         <v>0</v>
+      </c>
+      <c r="AU247" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV247" t="inlineStr">
         <is>
@@ -34841,6 +35666,11 @@
       <c r="R258" t="n">
         <v>0</v>
       </c>
+      <c r="S258" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA258" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -34853,12 +35683,22 @@
       </c>
       <c r="AP258" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR258" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS258" t="inlineStr"/>
       <c r="AT258" t="n">
         <v>0</v>
+      </c>
+      <c r="AU258" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV258" t="inlineStr">
         <is>
@@ -34976,6 +35816,11 @@
       <c r="R259" t="n">
         <v>0</v>
       </c>
+      <c r="S259" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA259" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -34988,12 +35833,22 @@
       </c>
       <c r="AP259" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR259" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS259" t="inlineStr"/>
       <c r="AT259" t="n">
         <v>0</v>
+      </c>
+      <c r="AU259" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV259" t="inlineStr">
         <is>
@@ -35102,6 +35957,11 @@
           <t>2026-06</t>
         </is>
       </c>
+      <c r="S260" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA260" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -35114,12 +35974,22 @@
       </c>
       <c r="AP260" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR260" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS260" t="inlineStr"/>
       <c r="AT260" t="n">
         <v>0</v>
+      </c>
+      <c r="AU260" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV260" t="inlineStr">
         <is>
@@ -35237,6 +36107,11 @@
       <c r="R261" t="n">
         <v>0</v>
       </c>
+      <c r="S261" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA261" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -35249,12 +36124,22 @@
       </c>
       <c r="AP261" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR261" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS261" t="inlineStr"/>
       <c r="AT261" t="n">
         <v>0</v>
+      </c>
+      <c r="AU261" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV261" t="inlineStr">
         <is>
@@ -35372,6 +36257,11 @@
       <c r="R262" t="n">
         <v>0</v>
       </c>
+      <c r="S262" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA262" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -35384,12 +36274,22 @@
       </c>
       <c r="AP262" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR262" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS262" t="inlineStr"/>
       <c r="AT262" t="n">
         <v>0</v>
+      </c>
+      <c r="AU262" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV262" t="inlineStr">
         <is>
@@ -35507,6 +36407,11 @@
       <c r="R263" t="n">
         <v>0</v>
       </c>
+      <c r="S263" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA263" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -35519,12 +36424,22 @@
       </c>
       <c r="AP263" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR263" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS263" t="inlineStr"/>
       <c r="AT263" t="n">
         <v>0</v>
+      </c>
+      <c r="AU263" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV263" t="inlineStr">
         <is>
@@ -35642,6 +36557,11 @@
       <c r="R264" t="n">
         <v>0</v>
       </c>
+      <c r="S264" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA264" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -35654,12 +36574,22 @@
       </c>
       <c r="AP264" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR264" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS264" t="inlineStr"/>
       <c r="AT264" t="n">
         <v>0</v>
+      </c>
+      <c r="AU264" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV264" t="inlineStr">
         <is>
@@ -35777,6 +36707,11 @@
       <c r="R265" t="n">
         <v>0</v>
       </c>
+      <c r="S265" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA265" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -35789,12 +36724,22 @@
       </c>
       <c r="AP265" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR265" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS265" t="inlineStr"/>
       <c r="AT265" t="n">
         <v>0</v>
+      </c>
+      <c r="AU265" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV265" t="inlineStr">
         <is>
@@ -35912,6 +36857,11 @@
       <c r="R266" t="n">
         <v>0</v>
       </c>
+      <c r="S266" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA266" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -35924,12 +36874,22 @@
       </c>
       <c r="AP266" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR266" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS266" t="inlineStr"/>
       <c r="AT266" t="n">
         <v>0</v>
+      </c>
+      <c r="AU266" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV266" t="inlineStr">
         <is>
@@ -41420,6 +42380,11 @@
       <c r="R308" t="n">
         <v>0</v>
       </c>
+      <c r="S308" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA308" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -41432,12 +42397,22 @@
       </c>
       <c r="AP308" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR308" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS308" t="inlineStr"/>
       <c r="AT308" t="n">
         <v>0</v>
+      </c>
+      <c r="AU308" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV308" t="inlineStr">
         <is>
@@ -41555,6 +42530,11 @@
       <c r="R309" t="n">
         <v>0</v>
       </c>
+      <c r="S309" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA309" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -41567,12 +42547,22 @@
       </c>
       <c r="AP309" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR309" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS309" t="inlineStr"/>
       <c r="AT309" t="n">
         <v>0</v>
+      </c>
+      <c r="AU309" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV309" t="inlineStr">
         <is>
@@ -42422,6 +43412,11 @@
       <c r="R315" t="n">
         <v>0</v>
       </c>
+      <c r="S315" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA315" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -42434,12 +43429,22 @@
       </c>
       <c r="AP315" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR315" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS315" t="inlineStr"/>
       <c r="AT315" t="n">
         <v>0</v>
+      </c>
+      <c r="AU315" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV315" t="inlineStr">
         <is>
@@ -42557,6 +43562,11 @@
       <c r="R316" t="n">
         <v>0</v>
       </c>
+      <c r="S316" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA316" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -42569,12 +43579,22 @@
       </c>
       <c r="AP316" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR316" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS316" t="inlineStr"/>
       <c r="AT316" t="n">
         <v>0</v>
+      </c>
+      <c r="AU316" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV316" t="inlineStr">
         <is>
@@ -42692,6 +43712,11 @@
       <c r="R317" t="n">
         <v>0</v>
       </c>
+      <c r="S317" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA317" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -42704,12 +43729,22 @@
       </c>
       <c r="AP317" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR317" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS317" t="inlineStr"/>
       <c r="AT317" t="n">
         <v>0</v>
+      </c>
+      <c r="AU317" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV317" t="inlineStr">
         <is>
@@ -42827,6 +43862,11 @@
       <c r="R318" t="n">
         <v>0</v>
       </c>
+      <c r="S318" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA318" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -42839,12 +43879,22 @@
       </c>
       <c r="AP318" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR318" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS318" t="inlineStr"/>
       <c r="AT318" t="n">
         <v>0</v>
+      </c>
+      <c r="AU318" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV318" t="inlineStr">
         <is>
@@ -42962,6 +44012,11 @@
       <c r="R319" t="n">
         <v>0</v>
       </c>
+      <c r="S319" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA319" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -42974,12 +44029,22 @@
       </c>
       <c r="AP319" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR319" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS319" t="inlineStr"/>
       <c r="AT319" t="n">
         <v>0</v>
+      </c>
+      <c r="AU319" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV319" t="inlineStr">
         <is>
@@ -43097,6 +44162,11 @@
       <c r="R320" t="n">
         <v>0</v>
       </c>
+      <c r="S320" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA320" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -43109,12 +44179,22 @@
       </c>
       <c r="AP320" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR320" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS320" t="inlineStr"/>
       <c r="AT320" t="n">
         <v>0</v>
+      </c>
+      <c r="AU320" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV320" t="inlineStr">
         <is>
@@ -43232,6 +44312,11 @@
       <c r="R321" t="n">
         <v>0</v>
       </c>
+      <c r="S321" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA321" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -43244,12 +44329,22 @@
       </c>
       <c r="AP321" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR321" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS321" t="inlineStr"/>
       <c r="AT321" t="n">
         <v>0</v>
+      </c>
+      <c r="AU321" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV321" t="inlineStr">
         <is>
@@ -43367,6 +44462,11 @@
       <c r="R322" t="n">
         <v>0</v>
       </c>
+      <c r="S322" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA322" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -43379,12 +44479,22 @@
       </c>
       <c r="AP322" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR322" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS322" t="inlineStr"/>
       <c r="AT322" t="n">
         <v>0</v>
+      </c>
+      <c r="AU322" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV322" t="inlineStr">
         <is>
@@ -43502,6 +44612,11 @@
       <c r="R323" t="n">
         <v>0</v>
       </c>
+      <c r="S323" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA323" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -43514,12 +44629,22 @@
       </c>
       <c r="AP323" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR323" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS323" t="inlineStr"/>
       <c r="AT323" t="n">
         <v>0</v>
+      </c>
+      <c r="AU323" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV323" t="inlineStr">
         <is>
@@ -49151,6 +50276,11 @@
       <c r="R366" t="n">
         <v>0</v>
       </c>
+      <c r="S366" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA366" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -49163,12 +50293,22 @@
       </c>
       <c r="AP366" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR366" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS366" t="inlineStr"/>
       <c r="AT366" t="n">
         <v>0</v>
+      </c>
+      <c r="AU366" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV366" t="inlineStr">
         <is>
@@ -49286,6 +50426,11 @@
       <c r="R367" t="n">
         <v>0.003875939847584092</v>
       </c>
+      <c r="S367" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA367" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -49298,12 +50443,22 @@
       </c>
       <c r="AP367" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR367" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS367" t="inlineStr"/>
       <c r="AT367" t="n">
         <v>0</v>
+      </c>
+      <c r="AU367" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV367" t="inlineStr">
         <is>
@@ -50144,6 +51299,11 @@
       <c r="R373" t="n">
         <v>0</v>
       </c>
+      <c r="S373" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA373" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -50156,12 +51316,22 @@
       </c>
       <c r="AP373" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR373" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS373" t="inlineStr"/>
       <c r="AT373" t="n">
         <v>0</v>
+      </c>
+      <c r="AU373" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV373" t="inlineStr">
         <is>
@@ -50279,6 +51449,11 @@
       <c r="R374" t="n">
         <v>0</v>
       </c>
+      <c r="S374" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA374" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -50291,12 +51466,22 @@
       </c>
       <c r="AP374" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR374" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS374" t="inlineStr"/>
       <c r="AT374" t="n">
         <v>0</v>
+      </c>
+      <c r="AU374" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV374" t="inlineStr">
         <is>
@@ -50414,6 +51599,11 @@
       <c r="R375" t="n">
         <v>0</v>
       </c>
+      <c r="S375" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA375" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -50426,12 +51616,22 @@
       </c>
       <c r="AP375" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR375" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS375" t="inlineStr"/>
       <c r="AT375" t="n">
         <v>0</v>
+      </c>
+      <c r="AU375" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV375" t="inlineStr">
         <is>
@@ -50549,6 +51749,11 @@
       <c r="R376" t="n">
         <v>0</v>
       </c>
+      <c r="S376" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA376" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -50561,12 +51766,22 @@
       </c>
       <c r="AP376" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR376" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS376" t="inlineStr"/>
       <c r="AT376" t="n">
         <v>0</v>
+      </c>
+      <c r="AU376" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV376" t="inlineStr">
         <is>
@@ -50684,6 +51899,11 @@
       <c r="R377" t="n">
         <v>0</v>
       </c>
+      <c r="S377" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA377" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -50696,12 +51916,22 @@
       </c>
       <c r="AP377" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR377" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS377" t="inlineStr"/>
       <c r="AT377" t="n">
         <v>0</v>
+      </c>
+      <c r="AU377" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV377" t="inlineStr">
         <is>
@@ -50819,6 +52049,11 @@
       <c r="R378" t="n">
         <v>0</v>
       </c>
+      <c r="S378" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA378" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -50831,12 +52066,22 @@
       </c>
       <c r="AP378" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR378" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS378" t="inlineStr"/>
       <c r="AT378" t="n">
         <v>0</v>
+      </c>
+      <c r="AU378" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV378" t="inlineStr">
         <is>
@@ -50954,6 +52199,11 @@
       <c r="R379" t="n">
         <v>0</v>
       </c>
+      <c r="S379" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA379" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -50966,12 +52216,22 @@
       </c>
       <c r="AP379" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR379" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS379" t="inlineStr"/>
       <c r="AT379" t="n">
         <v>0</v>
+      </c>
+      <c r="AU379" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV379" t="inlineStr">
         <is>
@@ -51089,6 +52349,11 @@
       <c r="R380" t="n">
         <v>0</v>
       </c>
+      <c r="S380" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA380" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -51101,12 +52366,22 @@
       </c>
       <c r="AP380" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR380" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS380" t="inlineStr"/>
       <c r="AT380" t="n">
         <v>0</v>
+      </c>
+      <c r="AU380" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV380" t="inlineStr">
         <is>
@@ -51224,6 +52499,11 @@
       <c r="R381" t="n">
         <v>0</v>
       </c>
+      <c r="S381" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA381" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -51236,12 +52516,22 @@
       </c>
       <c r="AP381" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR381" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS381" t="inlineStr"/>
       <c r="AT381" t="n">
         <v>0</v>
+      </c>
+      <c r="AU381" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV381" t="inlineStr">
         <is>
@@ -56444,6 +57734,11 @@
       <c r="R421" t="n">
         <v>0</v>
       </c>
+      <c r="S421" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA421" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -56456,12 +57751,22 @@
       </c>
       <c r="AP421" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR421" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS421" t="inlineStr"/>
       <c r="AT421" t="n">
         <v>0</v>
+      </c>
+      <c r="AU421" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV421" t="inlineStr">
         <is>
@@ -56579,6 +57884,11 @@
       <c r="R422" t="n">
         <v>0.001937969923792046</v>
       </c>
+      <c r="S422" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA422" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -56591,12 +57901,22 @@
       </c>
       <c r="AP422" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR422" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS422" t="inlineStr"/>
       <c r="AT422" t="n">
         <v>0</v>
+      </c>
+      <c r="AU422" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV422" t="inlineStr">
         <is>
@@ -57440,6 +58760,11 @@
       <c r="R428" t="n">
         <v>0.00367281181951979</v>
       </c>
+      <c r="S428" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA428" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -57452,12 +58777,22 @@
       </c>
       <c r="AP428" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR428" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS428" t="inlineStr"/>
       <c r="AT428" t="n">
         <v>0</v>
+      </c>
+      <c r="AU428" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV428" t="inlineStr">
         <is>
@@ -57575,6 +58910,11 @@
       <c r="R429" t="n">
         <v>0</v>
       </c>
+      <c r="S429" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA429" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -57587,12 +58927,22 @@
       </c>
       <c r="AP429" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR429" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS429" t="inlineStr"/>
       <c r="AT429" t="n">
         <v>0</v>
+      </c>
+      <c r="AU429" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV429" t="inlineStr">
         <is>
@@ -57710,6 +59060,11 @@
       <c r="R430" t="n">
         <v>0</v>
       </c>
+      <c r="S430" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA430" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -57722,12 +59077,22 @@
       </c>
       <c r="AP430" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR430" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS430" t="inlineStr"/>
       <c r="AT430" t="n">
         <v>0</v>
+      </c>
+      <c r="AU430" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV430" t="inlineStr">
         <is>
@@ -57845,6 +59210,11 @@
       <c r="R431" t="n">
         <v>0</v>
       </c>
+      <c r="S431" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA431" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -57857,12 +59227,22 @@
       </c>
       <c r="AP431" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR431" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS431" t="inlineStr"/>
       <c r="AT431" t="n">
         <v>0</v>
+      </c>
+      <c r="AU431" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV431" t="inlineStr">
         <is>
@@ -57980,6 +59360,11 @@
       <c r="R432" t="n">
         <v>0</v>
       </c>
+      <c r="S432" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA432" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -57992,12 +59377,22 @@
       </c>
       <c r="AP432" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR432" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS432" t="inlineStr"/>
       <c r="AT432" t="n">
         <v>0</v>
+      </c>
+      <c r="AU432" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV432" t="inlineStr">
         <is>
@@ -58115,6 +59510,11 @@
       <c r="R433" t="n">
         <v>0</v>
       </c>
+      <c r="S433" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA433" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -58127,12 +59527,22 @@
       </c>
       <c r="AP433" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR433" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS433" t="inlineStr"/>
       <c r="AT433" t="n">
         <v>0</v>
+      </c>
+      <c r="AU433" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV433" t="inlineStr">
         <is>
@@ -58250,6 +59660,11 @@
       <c r="R434" t="n">
         <v>0</v>
       </c>
+      <c r="S434" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA434" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -58262,12 +59677,22 @@
       </c>
       <c r="AP434" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR434" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS434" t="inlineStr"/>
       <c r="AT434" t="n">
         <v>0</v>
+      </c>
+      <c r="AU434" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV434" t="inlineStr">
         <is>
@@ -58385,6 +59810,11 @@
       <c r="R435" t="n">
         <v>0</v>
       </c>
+      <c r="S435" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA435" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -58397,12 +59827,22 @@
       </c>
       <c r="AP435" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR435" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS435" t="inlineStr"/>
       <c r="AT435" t="n">
         <v>0</v>
+      </c>
+      <c r="AU435" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV435" t="inlineStr">
         <is>
@@ -58520,6 +59960,11 @@
       <c r="R436" t="n">
         <v>0</v>
       </c>
+      <c r="S436" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA436" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -58532,12 +59977,22 @@
       </c>
       <c r="AP436" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR436" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS436" t="inlineStr"/>
       <c r="AT436" t="n">
         <v>0</v>
+      </c>
+      <c r="AU436" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV436" t="inlineStr">
         <is>
@@ -62709,12 +64164,12 @@
       </c>
       <c r="F469" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H469" t="inlineStr">
@@ -62748,13 +64203,18 @@
         </is>
       </c>
       <c r="N469" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O469" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R469" t="n">
-        <v>0.003875939847584092</v>
+        <v>0</v>
+      </c>
+      <c r="S469" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AA469" t="inlineStr">
         <is>
@@ -62768,51 +64228,61 @@
       </c>
       <c r="AP469" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR469" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS469" t="inlineStr"/>
       <c r="AT469" t="n">
         <v>0</v>
       </c>
+      <c r="AU469" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV469" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW469" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX469" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY469" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ469" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA469" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB469" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC469" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -62844,12 +64314,12 @@
       </c>
       <c r="F470" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H470" t="inlineStr">
@@ -62874,7 +64344,7 @@
       </c>
       <c r="L470" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M470" t="inlineStr">
@@ -62883,83 +64353,86 @@
         </is>
       </c>
       <c r="N470" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O470" t="n">
-        <v>1</v>
-      </c>
-      <c r="P470" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R470" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="U470" t="inlineStr">
-        <is>
-          <t>HOLD_US_23efe3522b8141a771af70d76b4d</t>
+        <v>0.003875939847584092</v>
+      </c>
+      <c r="S470" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA470" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO470" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP470" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS470" t="inlineStr">
-        <is>
-          <t>HOLD_US_23efe3522b8141a771af70d76b4d</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR470" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS470" t="inlineStr"/>
       <c r="AT470" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AU470" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV470" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW470" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX470" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY470" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ470" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA470" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB470" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC470" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -62991,12 +64464,12 @@
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>US-FL</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>Florida, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H471" t="inlineStr">
@@ -63038,6 +64511,9 @@
       <c r="P471" t="n">
         <v>1</v>
       </c>
+      <c r="R471" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
       <c r="U471" t="inlineStr">
         <is>
           <t>HOLD_US_23efe3522b8141a771af70d76b4d</t>
@@ -63050,7 +64526,7 @@
       </c>
       <c r="AO471" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP471" t="inlineStr">
@@ -63078,32 +64554,32 @@
       </c>
       <c r="AX471" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY471" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ471" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA471" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB471" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC471" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -63135,12 +64611,12 @@
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>US-FL</t>
         </is>
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Florida, United States</t>
         </is>
       </c>
       <c r="H472" t="inlineStr">
@@ -63165,7 +64641,7 @@
       </c>
       <c r="L472" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="M472" t="inlineStr">
@@ -63182,9 +64658,6 @@
       <c r="P472" t="n">
         <v>1</v>
       </c>
-      <c r="R472" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
       <c r="U472" t="inlineStr">
         <is>
           <t>HOLD_US_23efe3522b8141a771af70d76b4d</t>
@@ -63197,7 +64670,7 @@
       </c>
       <c r="AO472" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP472" t="inlineStr">
@@ -63225,32 +64698,32 @@
       </c>
       <c r="AX472" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY472" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ472" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA472" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB472" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC472" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -63282,12 +64755,12 @@
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>US-FL</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>Florida, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H473" t="inlineStr">
@@ -63329,6 +64802,9 @@
       <c r="P473" t="n">
         <v>1</v>
       </c>
+      <c r="R473" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
       <c r="U473" t="inlineStr">
         <is>
           <t>HOLD_US_23efe3522b8141a771af70d76b4d</t>
@@ -63341,7 +64817,7 @@
       </c>
       <c r="AO473" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP473" t="inlineStr">
@@ -63369,32 +64845,32 @@
       </c>
       <c r="AX473" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY473" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ473" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA473" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB473" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC473" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -63426,12 +64902,12 @@
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US-FL</t>
         </is>
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Florida, United States</t>
         </is>
       </c>
       <c r="H474" t="inlineStr">
@@ -63456,31 +64932,36 @@
       </c>
       <c r="L474" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N474" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O474" t="n">
-        <v>0</v>
-      </c>
-      <c r="R474" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P474" t="n">
+        <v>1</v>
+      </c>
+      <c r="U474" t="inlineStr">
+        <is>
+          <t>HOLD_US_23efe3522b8141a771af70d76b4d</t>
+        </is>
       </c>
       <c r="AA474" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO474" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP474" t="inlineStr">
@@ -63488,48 +64969,52 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS474" t="inlineStr"/>
+      <c r="AS474" t="inlineStr">
+        <is>
+          <t>HOLD_US_23efe3522b8141a771af70d76b4d</t>
+        </is>
+      </c>
       <c r="AT474" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV474" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW474" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX474" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY474" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ474" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA474" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB474" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC474" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -63561,12 +65046,12 @@
       </c>
       <c r="F475" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H475" t="inlineStr">
@@ -63608,6 +65093,11 @@
       <c r="R475" t="n">
         <v>0</v>
       </c>
+      <c r="S475" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA475" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -63620,51 +65110,61 @@
       </c>
       <c r="AP475" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR475" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS475" t="inlineStr"/>
       <c r="AT475" t="n">
         <v>0</v>
       </c>
+      <c r="AU475" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV475" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW475" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX475" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY475" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ475" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA475" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB475" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC475" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -63696,12 +65196,12 @@
       </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H476" t="inlineStr">
@@ -63726,7 +65226,7 @@
       </c>
       <c r="L476" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="M476" t="inlineStr">
@@ -63735,83 +65235,86 @@
         </is>
       </c>
       <c r="N476" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O476" t="n">
-        <v>1</v>
-      </c>
-      <c r="P476" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R476" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="U476" t="inlineStr">
-        <is>
-          <t>HOLD_US_23efe3522b8141a771af70d76b4d</t>
+        <v>0</v>
+      </c>
+      <c r="S476" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA476" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO476" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP476" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS476" t="inlineStr">
-        <is>
-          <t>HOLD_US_23efe3522b8141a771af70d76b4d</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR476" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS476" t="inlineStr"/>
       <c r="AT476" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AU476" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV476" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW476" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX476" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY476" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ476" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA476" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB476" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC476" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -63843,12 +65346,12 @@
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>US-FL</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>Florida, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H477" t="inlineStr">
@@ -63890,6 +65393,9 @@
       <c r="P477" t="n">
         <v>1</v>
       </c>
+      <c r="R477" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
       <c r="U477" t="inlineStr">
         <is>
           <t>HOLD_US_23efe3522b8141a771af70d76b4d</t>
@@ -63902,7 +65408,7 @@
       </c>
       <c r="AO477" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP477" t="inlineStr">
@@ -63930,32 +65436,32 @@
       </c>
       <c r="AX477" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY477" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ477" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA477" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB477" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC477" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -63987,12 +65493,12 @@
       </c>
       <c r="F478" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>US-FL</t>
         </is>
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Florida, United States</t>
         </is>
       </c>
       <c r="H478" t="inlineStr">
@@ -64017,7 +65523,7 @@
       </c>
       <c r="L478" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="M478" t="inlineStr">
@@ -64034,9 +65540,6 @@
       <c r="P478" t="n">
         <v>1</v>
       </c>
-      <c r="R478" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
       <c r="U478" t="inlineStr">
         <is>
           <t>HOLD_US_23efe3522b8141a771af70d76b4d</t>
@@ -64049,7 +65552,7 @@
       </c>
       <c r="AO478" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP478" t="inlineStr">
@@ -64077,32 +65580,32 @@
       </c>
       <c r="AX478" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY478" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ478" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA478" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB478" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC478" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -64134,12 +65637,12 @@
       </c>
       <c r="F479" t="inlineStr">
         <is>
-          <t>US-FL</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G479" t="inlineStr">
         <is>
-          <t>Florida, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H479" t="inlineStr">
@@ -64181,6 +65684,9 @@
       <c r="P479" t="n">
         <v>1</v>
       </c>
+      <c r="R479" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
       <c r="U479" t="inlineStr">
         <is>
           <t>HOLD_US_23efe3522b8141a771af70d76b4d</t>
@@ -64193,7 +65699,7 @@
       </c>
       <c r="AO479" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP479" t="inlineStr">
@@ -64221,30 +65727,174 @@
       </c>
       <c r="AX479" t="inlineStr">
         <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY479" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ479" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA479" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB479" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC479" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>leprosy</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>US-FL</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>Florida, United States</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="J480" t="inlineStr">
+        <is>
+          <t>麻风病</t>
+        </is>
+      </c>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L480" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M480" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N480" t="n">
+        <v>1</v>
+      </c>
+      <c r="O480" t="n">
+        <v>1</v>
+      </c>
+      <c r="P480" t="n">
+        <v>1</v>
+      </c>
+      <c r="U480" t="inlineStr">
+        <is>
+          <t>HOLD_US_23efe3522b8141a771af70d76b4d</t>
+        </is>
+      </c>
+      <c r="AA480" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO480" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP480" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS480" t="inlineStr">
+        <is>
+          <t>HOLD_US_23efe3522b8141a771af70d76b4d</t>
+        </is>
+      </c>
+      <c r="AT480" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV480" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW480" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX480" t="inlineStr">
+        <is>
           <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
-      <c r="AY479" t="inlineStr">
+      <c r="AY480" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ479" t="inlineStr">
+      <c r="AZ480" t="inlineStr">
         <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="BA479" t="inlineStr">
+      <c r="BA480" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="BB479" t="inlineStr">
+      <c r="BB480" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
-      <c r="BC479" t="inlineStr">
+      <c r="BC480" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -64366,7 +66016,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="10">
@@ -64376,7 +66026,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="11">
